--- a/Staff Name and Account Name.xlsx
+++ b/Staff Name and Account Name.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cigpsa-my.sharepoint.com/personal/kate_zhang_cigp_com/Documents/Desktop/PAD Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_AD4DB114E441178AC67DF4A0B614CE12693EDF1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{485A21F9-A4E0-4A4F-963C-B70C4CF83AFD}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="11_AD4DB114E441178AC67DF4A0B614CE12693EDF1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9E8A7C4-E88D-4D13-B4E1-DD136BA04B32}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="94">
   <si>
     <t>Staff Names as per CIGP</t>
   </si>
@@ -304,6 +315,9 @@
   </si>
   <si>
     <t>Guillaume Boris Page</t>
+  </si>
+  <si>
+    <t>Kobe Yip</t>
   </si>
 </sst>
 </file>
@@ -454,6 +468,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -719,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" style="8" bestFit="1" customWidth="1"/>
@@ -1130,6 +1148,11 @@
       </c>
       <c r="B51" s="6" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
